--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{04996141-9810-4DFC-B393-8EC5F7C79486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{52297398-AEED-4D27-8B79-5C105A3A5343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="387">
   <si>
     <t>Manager</t>
   </si>
@@ -1195,9 +1195,6 @@
   </si>
   <si>
     <t>Winnipeg Jets</t>
-  </si>
-  <si>
-    <t>LA Clippers</t>
   </si>
 </sst>
 </file>
@@ -6982,7 +6979,7 @@
         <v>4</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{52297398-AEED-4D27-8B79-5C105A3A5343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C324991C-78DF-4980-86D8-CF1DE48DD6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -531,9 +530,6 @@
     <t>Auston Matthews</t>
   </si>
   <si>
-    <t>Logan Thompson</t>
-  </si>
-  <si>
     <t>Kirill Kaprizov</t>
   </si>
   <si>
@@ -711,9 +707,6 @@
     <t>Aleksander Barkov</t>
   </si>
   <si>
-    <t>Connor Hellebuyck</t>
-  </si>
-  <si>
     <t>Matt Fitzpatrick</t>
   </si>
   <si>
@@ -1194,7 +1187,13 @@
     <t>San Diego FC</t>
   </si>
   <si>
-    <t>Winnipeg Jets</t>
+    <t>Cole Hutson</t>
+  </si>
+  <si>
+    <t>Porter Martone</t>
+  </si>
+  <si>
+    <t>Philadelphia Flyers</t>
   </si>
 </sst>
 </file>
@@ -1562,19 +1561,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1585,16 +1584,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>174</v>
@@ -1605,22 +1604,22 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1631,19 +1630,19 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
       <c r="G5" t="s">
-        <v>233</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1654,19 +1653,19 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1677,19 +1676,19 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1700,19 +1699,19 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1720,22 +1719,22 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1743,22 +1742,22 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F10">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1769,7 +1768,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -1778,10 +1777,10 @@
         <v>23</v>
       </c>
       <c r="F11">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>332</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1792,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -1801,10 +1800,10 @@
         <v>23</v>
       </c>
       <c r="F12">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1815,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
@@ -1824,10 +1823,10 @@
         <v>23</v>
       </c>
       <c r="F13">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>295</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1838,19 +1837,19 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1858,22 +1857,22 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1881,22 +1880,22 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1907,19 +1906,19 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1930,19 +1929,19 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>325</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1950,22 +1949,22 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F19">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>335</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1973,22 +1972,22 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>304</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1999,19 +1998,19 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>336</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2022,19 +2021,19 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="G22" t="s">
-        <v>134</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -2045,19 +2044,19 @@
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -2068,19 +2067,19 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F24">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2088,22 +2087,22 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -2111,22 +2110,22 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F26">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -2134,22 +2133,22 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F27">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>337</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -2157,22 +2156,22 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>327</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="F28">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2180,22 +2179,22 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="F29">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="G29" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2203,22 +2202,22 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G30" t="s">
-        <v>339</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -2226,22 +2225,22 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="G31" t="s">
-        <v>340</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -2249,22 +2248,22 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="F32">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>341</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -2275,19 +2274,19 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>310</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2298,19 +2297,19 @@
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>245</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>57</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2318,22 +2317,22 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F35">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2341,45 +2340,45 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>254</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F37">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2387,22 +2386,22 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>309</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>61</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2413,19 +2412,19 @@
         <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -2436,19 +2435,19 @@
         <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -2456,22 +2455,22 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F41">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -2479,22 +2478,22 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F42">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G42" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2502,22 +2501,22 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F43">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2525,22 +2524,22 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F44">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -2551,19 +2550,19 @@
         <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D45" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2574,19 +2573,19 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="F46">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -2594,22 +2593,22 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="F47">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="G47" t="s">
-        <v>76</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2617,22 +2616,22 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="F48">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="G48" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2640,22 +2639,22 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F49">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="G49" t="s">
-        <v>79</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -2663,22 +2662,22 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2686,22 +2685,22 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2709,229 +2708,229 @@
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E52" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F52">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G52" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F53">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>308</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F54">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="G54" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D55" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F55">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G55" t="s">
-        <v>343</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>87</v>
+        <v>319</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>344</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
         <v>18</v>
       </c>
       <c r="F57">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G57" t="s">
-        <v>236</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>318</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="E58" t="s">
         <v>18</v>
       </c>
       <c r="F58">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>177</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D59" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F59">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s">
-        <v>292</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="F60">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G60" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="B61" t="s">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F61">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2942,19 +2941,19 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F62">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -2965,19 +2964,19 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F63">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>347</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -2985,22 +2984,22 @@
         <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F64">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G64" t="s">
-        <v>294</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -3008,22 +3007,22 @@
         <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F65">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="G65" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -3034,19 +3033,19 @@
         <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D66" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F66">
         <v>100</v>
       </c>
       <c r="G66" t="s">
-        <v>348</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -3057,19 +3056,19 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D67" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F67">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -3080,19 +3079,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>315</v>
       </c>
       <c r="D68" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>349</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -3100,22 +3099,22 @@
         <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D69" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F69">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G69" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -3123,22 +3122,22 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C70" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D70" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F70">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>350</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
@@ -3149,19 +3148,19 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F71">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G71" t="s">
-        <v>253</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -3172,19 +3171,19 @@
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F72">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
@@ -3192,22 +3191,22 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C73" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F73">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G73" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -3215,22 +3214,22 @@
         <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E74" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="F74">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G74" t="s">
-        <v>352</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -3241,19 +3240,19 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D75" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F75">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G75" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -3264,19 +3263,19 @@
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D76" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E76" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F76">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G76" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -3287,19 +3286,19 @@
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77">
         <v>50</v>
       </c>
-      <c r="E77" t="s">
-        <v>51</v>
-      </c>
-      <c r="F77">
-        <v>15</v>
-      </c>
       <c r="G77" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -3310,19 +3309,19 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E78" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F78">
         <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>355</v>
+        <v>292</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -3330,22 +3329,22 @@
         <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C79" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D79" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E79" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G79" t="s">
-        <v>338</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -3356,19 +3355,19 @@
         <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F80">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -3376,22 +3375,22 @@
         <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>113</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
@@ -3399,22 +3398,22 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G82" t="s">
-        <v>114</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -3445,22 +3444,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>323</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F84">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -3468,22 +3467,22 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>117</v>
+        <v>324</v>
       </c>
       <c r="D85" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F85">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>117</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -3491,22 +3490,22 @@
         <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F86">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="G86" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
@@ -3514,22 +3513,22 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F87">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G87" t="s">
-        <v>119</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -3537,22 +3536,22 @@
         <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>120</v>
+        <v>313</v>
       </c>
       <c r="D88" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E88" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F88">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>120</v>
+        <v>368</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -3560,22 +3559,22 @@
         <v>83</v>
       </c>
       <c r="B89" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>121</v>
+        <v>314</v>
       </c>
       <c r="D89" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E89" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F89">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -3586,19 +3585,19 @@
         <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E90" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F90">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G90" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -3609,19 +3608,19 @@
         <v>55</v>
       </c>
       <c r="C91" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D91" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E91" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F91">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G91" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -3632,19 +3631,19 @@
         <v>55</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D92" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E92" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F92">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
@@ -3655,19 +3654,19 @@
         <v>55</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>328</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="E93" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="F93">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G93" t="s">
-        <v>125</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -3678,19 +3677,19 @@
         <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D94" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E94" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F94">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -3701,19 +3700,19 @@
         <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>330</v>
+        <v>129</v>
       </c>
       <c r="D95" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="E95" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="F95">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G95" t="s">
-        <v>330</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
@@ -3724,19 +3723,19 @@
         <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E96" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F96">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="G96" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
@@ -3747,19 +3746,19 @@
         <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F97">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="G97" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -3770,19 +3769,19 @@
         <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D98" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E98" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F98">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -3793,19 +3792,19 @@
         <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D99" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E99" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F99">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G99" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -3813,22 +3812,22 @@
         <v>83</v>
       </c>
       <c r="B100" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E100" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F100">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -3836,22 +3835,22 @@
         <v>83</v>
       </c>
       <c r="B101" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E101" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F101">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>133</v>
+        <v>347</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -3859,10 +3858,10 @@
         <v>83</v>
       </c>
       <c r="B102" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="D102" t="s">
         <v>37</v>
@@ -3871,10 +3870,10 @@
         <v>37</v>
       </c>
       <c r="F102">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="G102" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
@@ -3882,10 +3881,10 @@
         <v>83</v>
       </c>
       <c r="B103" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
         <v>37</v>
@@ -3894,10 +3893,10 @@
         <v>37</v>
       </c>
       <c r="F103">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
@@ -3908,19 +3907,19 @@
         <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D104" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E104" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F104">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="G104" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
@@ -3931,237 +3930,237 @@
         <v>55</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D105" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E105" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F105">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G105" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B106" t="s">
         <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E106" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F106">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G106" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="D107" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E107" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F107">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G107" t="s">
-        <v>174</v>
+        <v>349</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D108" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E108" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F108">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G108" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="D109" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E109" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>112</v>
+        <v>350</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E110" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G110" t="s">
-        <v>356</v>
+        <v>136</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D111" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E111" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F111">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G111" t="s">
-        <v>291</v>
+        <v>137</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="D112" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="E112" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F112">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G112" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="D113" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="E113" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F113">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>236</v>
+        <v>351</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>312</v>
       </c>
       <c r="D114" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E114" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F114">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>58</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>254</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="D115" t="s">
         <v>17</v>
@@ -4170,148 +4169,148 @@
         <v>18</v>
       </c>
       <c r="F115">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G115" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="D116" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E116" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F116">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B117" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D117" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E117" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F117">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>357</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B118" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="D118" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E118" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F118">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G118" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E119" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F119">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G119" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="D120" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E120" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="F120">
         <v>5</v>
       </c>
       <c r="G120" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B121" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="D121" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="E121" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F121">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G121" t="s">
-        <v>338</v>
+        <v>121</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
@@ -4322,19 +4321,19 @@
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D122" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E122" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F122">
         <v>90</v>
       </c>
       <c r="G122" t="s">
-        <v>296</v>
+        <v>352</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
@@ -4345,19 +4344,19 @@
         <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F123">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G123" t="s">
-        <v>359</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
@@ -4368,19 +4367,19 @@
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F124">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
@@ -4388,22 +4387,22 @@
         <v>138</v>
       </c>
       <c r="B125" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D125" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F125">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G125" t="s">
-        <v>361</v>
+        <v>174</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
@@ -4414,19 +4413,19 @@
         <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D126" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E126" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F126">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="G126" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -4437,19 +4436,19 @@
         <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D127" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E127" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F127">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G127" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
@@ -4460,19 +4459,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D128" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E128" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F128">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G128" t="s">
-        <v>363</v>
+        <v>234</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
@@ -4483,19 +4482,19 @@
         <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="D129" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E129" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F129">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G129" t="s">
-        <v>364</v>
+        <v>173</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
@@ -4506,19 +4505,19 @@
         <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D130" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E130" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G130" t="s">
-        <v>365</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
@@ -4526,22 +4525,22 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C131" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D131" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E131" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G131" t="s">
-        <v>252</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -4549,22 +4548,22 @@
         <v>138</v>
       </c>
       <c r="B132" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C132" t="s">
-        <v>166</v>
+        <v>306</v>
       </c>
       <c r="D132" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E132" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F132">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>352</v>
+        <v>306</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
@@ -4575,19 +4574,19 @@
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D133" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E133" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F133">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="G133" t="s">
-        <v>352</v>
+        <v>181</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
@@ -4598,19 +4597,19 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D134" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E134" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F134">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G134" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
@@ -4621,19 +4620,19 @@
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D135" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F135">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G135" t="s">
-        <v>338</v>
+        <v>182</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
@@ -4644,19 +4643,19 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D136" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E136" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -4664,22 +4663,22 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C137" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D137" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E137" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F137">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="G137" t="s">
-        <v>354</v>
+        <v>181</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
@@ -4687,22 +4686,22 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C138" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D138" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="E138" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F138">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="G138" t="s">
-        <v>338</v>
+        <v>182</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
@@ -4713,19 +4712,19 @@
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D139" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="E139" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F139">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G139" t="s">
-        <v>366</v>
+        <v>232</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -4736,19 +4735,19 @@
         <v>55</v>
       </c>
       <c r="C140" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
       </c>
       <c r="F140">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
@@ -4756,22 +4755,22 @@
         <v>138</v>
       </c>
       <c r="B141" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F141">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G141" t="s">
-        <v>175</v>
+        <v>336</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -4779,22 +4778,22 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C142" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F142">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="G142" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
@@ -4802,22 +4801,22 @@
         <v>138</v>
       </c>
       <c r="B143" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D143" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E143" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F143">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G143" t="s">
-        <v>177</v>
+        <v>357</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
@@ -4825,22 +4824,22 @@
         <v>138</v>
       </c>
       <c r="B144" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C144" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="D144" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="E144" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F144">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G144" t="s">
-        <v>178</v>
+        <v>358</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
@@ -4848,22 +4847,22 @@
         <v>138</v>
       </c>
       <c r="B145" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C145" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="D145" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="E145" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F145">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G145" t="s">
-        <v>179</v>
+        <v>359</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
@@ -4874,19 +4873,19 @@
         <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D146" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="E146" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F146">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="G146" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -4897,19 +4896,19 @@
         <v>55</v>
       </c>
       <c r="C147" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D147" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E147" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F147">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G147" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
@@ -4920,19 +4919,19 @@
         <v>55</v>
       </c>
       <c r="C148" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="D148" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E148" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F148">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -4943,19 +4942,19 @@
         <v>55</v>
       </c>
       <c r="C149" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D149" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="E149" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="F149">
-        <v>175</v>
+        <v>11</v>
       </c>
       <c r="G149" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
@@ -4966,19 +4965,19 @@
         <v>55</v>
       </c>
       <c r="C150" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D150" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E150" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F150">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G150" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
@@ -4989,19 +4988,19 @@
         <v>55</v>
       </c>
       <c r="C151" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D151" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="E151" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F151">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="G151" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
@@ -5012,19 +5011,19 @@
         <v>55</v>
       </c>
       <c r="C152" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D152" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E152" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F152">
         <v>5</v>
       </c>
       <c r="G152" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -5035,19 +5034,19 @@
         <v>55</v>
       </c>
       <c r="C153" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D153" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E153" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
@@ -5058,19 +5057,19 @@
         <v>55</v>
       </c>
       <c r="C154" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D154" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E154" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F154">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G154" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5081,19 +5080,19 @@
         <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D155" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="E155" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="F155">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G155" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
@@ -5101,22 +5100,22 @@
         <v>138</v>
       </c>
       <c r="B156" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C156" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D156" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="E156" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F156">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="G156" t="s">
-        <v>189</v>
+        <v>360</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5124,22 +5123,22 @@
         <v>138</v>
       </c>
       <c r="B157" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C157" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D157" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E157" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="F157">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>190</v>
+        <v>303</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
@@ -5147,22 +5146,22 @@
         <v>138</v>
       </c>
       <c r="B158" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C158" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="D158" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E158" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="F158">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G158" t="s">
-        <v>191</v>
+        <v>361</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
@@ -5170,22 +5169,22 @@
         <v>138</v>
       </c>
       <c r="B159" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C159" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D159" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E159" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F159">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G159" t="s">
-        <v>192</v>
+        <v>362</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
@@ -5199,13 +5198,13 @@
         <v>193</v>
       </c>
       <c r="D160" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E160" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F160">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G160" t="s">
         <v>193</v>
@@ -5228,7 +5227,7 @@
         <v>37</v>
       </c>
       <c r="F161">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="G161" t="s">
         <v>194</v>
@@ -5239,22 +5238,22 @@
         <v>138</v>
       </c>
       <c r="B162" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C162" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="D162" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E162" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F162">
-        <v>141</v>
+        <v>2</v>
       </c>
       <c r="G162" t="s">
-        <v>195</v>
+        <v>363</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
@@ -5262,10 +5261,10 @@
         <v>138</v>
       </c>
       <c r="B163" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C163" t="s">
-        <v>196</v>
+        <v>384</v>
       </c>
       <c r="D163" t="s">
         <v>41</v>
@@ -5274,10 +5273,10 @@
         <v>41</v>
       </c>
       <c r="F163">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G163" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
@@ -5285,10 +5284,10 @@
         <v>138</v>
       </c>
       <c r="B164" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C164" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="D164" t="s">
         <v>41</v>
@@ -5297,159 +5296,159 @@
         <v>41</v>
       </c>
       <c r="F164">
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="G164" t="s">
-        <v>197</v>
+        <v>350</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B165" t="s">
         <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="D165" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E165" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F165">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="G165" t="s">
-        <v>175</v>
+        <v>350</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B166" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C166" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D166" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E166" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F166">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G166" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B167" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C167" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E167" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F167">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="G167" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B168" t="s">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E168" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F168">
         <v>30</v>
       </c>
       <c r="G168" t="s">
-        <v>234</v>
+        <v>336</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B169" t="s">
         <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="D169" t="s">
+        <v>46</v>
+      </c>
+      <c r="E169" t="s">
+        <v>46</v>
+      </c>
+      <c r="F169">
         <v>15</v>
       </c>
-      <c r="E169" t="s">
-        <v>10</v>
-      </c>
-      <c r="F169">
-        <v>30</v>
-      </c>
       <c r="G169" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B170" t="s">
         <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E170" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F170">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>235</v>
+        <v>336</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B171" t="s">
         <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -5458,21 +5457,21 @@
         <v>18</v>
       </c>
       <c r="F171">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G171" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B172" t="s">
         <v>7</v>
       </c>
       <c r="C172" t="s">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="D172" t="s">
         <v>17</v>
@@ -5481,260 +5480,260 @@
         <v>18</v>
       </c>
       <c r="F172">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G172" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B173" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C173" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="D173" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="E173" t="s">
         <v>18</v>
       </c>
       <c r="F173">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G173" t="s">
-        <v>367</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B174" t="s">
         <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>208</v>
+        <v>320</v>
       </c>
       <c r="D174" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="E174" t="s">
         <v>18</v>
       </c>
       <c r="F174">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G174" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B175" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C175" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E175" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F175">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="G175" t="s">
-        <v>368</v>
+        <v>177</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B176" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C176" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="D176" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E176" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F176">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="G176" t="s">
-        <v>345</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B177" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C177" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D177" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E177" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F177">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G177" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B178" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C178" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="D178" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="E178" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F178">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G178" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B179" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C179" t="s">
-        <v>213</v>
+        <v>63</v>
       </c>
       <c r="D179" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="E179" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F179">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G179" t="s">
-        <v>369</v>
+        <v>63</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="D180" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E180" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="F180">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="G180" t="s">
-        <v>63</v>
+        <v>336</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="D181" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E181" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F181">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G181" t="s">
-        <v>124</v>
+        <v>364</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D182" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E182" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F182">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="G182" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D183" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E183" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F183">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G183" t="s">
         <v>370</v>
@@ -5742,358 +5741,358 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
+        <v>197</v>
+      </c>
+      <c r="B184" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" t="s">
         <v>198</v>
       </c>
-      <c r="B184" t="s">
-        <v>7</v>
-      </c>
-      <c r="C184" t="s">
-        <v>218</v>
-      </c>
       <c r="D184" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F184">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G184" t="s">
-        <v>250</v>
+        <v>174</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D185" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F185">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G185" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B186" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C186" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="D186" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="E186" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F186">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G186" t="s">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B187" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C187" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D187" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E187" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F187">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G187" t="s">
-        <v>371</v>
+        <v>229</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B188" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C188" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D188" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E188" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F188">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G188" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B189" t="s">
         <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D189" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E189" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F189">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G189" t="s">
-        <v>253</v>
+        <v>366</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B190" t="s">
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D190" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E190" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F190">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G190" t="s">
-        <v>196</v>
+        <v>343</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D191" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E191" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F191">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G191" t="s">
-        <v>386</v>
+        <v>122</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B192" t="s">
         <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D192" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E192" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F192">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G192" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B193" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C193" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D193" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E193" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F193">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G193" t="s">
-        <v>338</v>
+        <v>238</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B194" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D194" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E194" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F194">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G194" t="s">
-        <v>66</v>
+        <v>239</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="D195" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="E195" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F195">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G195" t="s">
-        <v>338</v>
+        <v>175</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B196" t="s">
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="D196" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E196" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F196">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G196" t="s">
-        <v>372</v>
+        <v>231</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="D197" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
       </c>
       <c r="F197">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G197" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C198" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="D198" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
       </c>
       <c r="F198">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G198" t="s">
-        <v>232</v>
+        <v>286</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B199" t="s">
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -6105,18 +6104,18 @@
         <v>100</v>
       </c>
       <c r="G199" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B200" t="s">
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -6128,150 +6127,150 @@
         <v>75</v>
       </c>
       <c r="G200" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B201" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="D201" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E201" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F201">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="G201" t="s">
-        <v>235</v>
+        <v>367</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B202" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C202" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="D202" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="E202" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F202">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G202" t="s">
-        <v>236</v>
+        <v>63</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B203" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C203" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="D203" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E203" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F203">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G203" t="s">
-        <v>237</v>
+        <v>124</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B204" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="D204" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E204" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F204">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G204" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B205" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="D205" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E205" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F205">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G205" t="s">
-        <v>120</v>
+        <v>368</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B206" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C206" t="s">
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="D206" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E206" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F206">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G206" t="s">
-        <v>239</v>
+        <v>380</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B207" t="s">
         <v>55</v>
@@ -6280,13 +6279,13 @@
         <v>240</v>
       </c>
       <c r="D207" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E207" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F207">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G207" t="s">
         <v>240</v>
@@ -6294,7 +6293,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B208" t="s">
         <v>55</v>
@@ -6303,13 +6302,13 @@
         <v>241</v>
       </c>
       <c r="D208" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E208" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F208">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G208" t="s">
         <v>241</v>
@@ -6317,7 +6316,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B209" t="s">
         <v>55</v>
@@ -6326,13 +6325,13 @@
         <v>242</v>
       </c>
       <c r="D209" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E209" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F209">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G209" t="s">
         <v>242</v>
@@ -6340,59 +6339,59 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B210" t="s">
         <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>243</v>
+        <v>321</v>
       </c>
       <c r="D210" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="E210" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="F210">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G210" t="s">
-        <v>243</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B211" t="s">
         <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D211" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E211" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F211">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G211" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B212" t="s">
         <v>55</v>
       </c>
       <c r="C212" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="D212" t="s">
         <v>75</v>
@@ -6401,21 +6400,21 @@
         <v>75</v>
       </c>
       <c r="F212">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G212" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B213" t="s">
         <v>55</v>
       </c>
       <c r="C213" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D213" t="s">
         <v>78</v>
@@ -6427,18 +6426,18 @@
         <v>10</v>
       </c>
       <c r="G213" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B214" t="s">
         <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D214" t="s">
         <v>78</v>
@@ -6450,18 +6449,18 @@
         <v>10</v>
       </c>
       <c r="G214" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B215" t="s">
         <v>55</v>
       </c>
       <c r="C215" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D215" t="s">
         <v>132</v>
@@ -6473,18 +6472,18 @@
         <v>100</v>
       </c>
       <c r="G215" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B216" t="s">
         <v>55</v>
       </c>
       <c r="C216" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D216" t="s">
         <v>132</v>
@@ -6496,18 +6495,18 @@
         <v>75</v>
       </c>
       <c r="G216" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B217" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="D217" t="s">
         <v>37</v>
@@ -6516,21 +6515,21 @@
         <v>37</v>
       </c>
       <c r="F217">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G217" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B218" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C218" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D218" t="s">
         <v>37</v>
@@ -6539,912 +6538,912 @@
         <v>37</v>
       </c>
       <c r="F218">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G218" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B219" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C219" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="D219" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E219" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F219">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G219" t="s">
-        <v>252</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B220" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C220" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D220" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E220" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F220">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G220" t="s">
-        <v>253</v>
+        <v>369</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B221" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C221" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D221" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E221" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F221">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="G221" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B222" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C222" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D222" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E222" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F222">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G222" t="s">
-        <v>175</v>
+        <v>249</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B223" t="s">
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="D223" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E223" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F223">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G223" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B224" t="s">
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="D224" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E224" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F224">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G224" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B225" t="s">
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="D225" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E225" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="F225">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="G225" t="s">
-        <v>374</v>
+        <v>195</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B226" t="s">
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>260</v>
+        <v>385</v>
       </c>
       <c r="D226" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E226" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F226">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G226" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B227" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C227" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="D227" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="E227" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F227">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G227" t="s">
-        <v>376</v>
+        <v>250</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B228" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C228" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D228" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="E228" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F228">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="G228" t="s">
-        <v>377</v>
+        <v>251</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="D229" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E229" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F229">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G229" t="s">
-        <v>378</v>
+        <v>120</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
       </c>
       <c r="C230" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="D230" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E230" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F230">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G230" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="D231" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E231" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G231" t="s">
-        <v>378</v>
+        <v>120</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B232" t="s">
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="D232" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E232" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F232">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="G232" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B233" t="s">
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="D233" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="E233" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F233">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G233" t="s">
-        <v>338</v>
+        <v>233</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B234" t="s">
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="D234" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E234" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F234">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="G234" t="s">
-        <v>369</v>
+        <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B235" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C235" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="D235" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E235" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F235">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="G235" t="s">
-        <v>70</v>
+        <v>233</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B236" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C236" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="D236" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E236" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F236">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="G236" t="s">
-        <v>379</v>
+        <v>235</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B237" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C237" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="D237" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E237" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F237">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G237" t="s">
-        <v>382</v>
+        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B238" t="s">
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
       <c r="D238" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="E238" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G238" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B239" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C239" t="s">
-        <v>273</v>
+        <v>120</v>
       </c>
       <c r="D239" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="E239" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F239">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G239" t="s">
-        <v>194</v>
+        <v>120</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B240" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C240" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="D240" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="E240" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F240">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G240" t="s">
-        <v>362</v>
+        <v>237</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="B241" t="s">
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="D241" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E241" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F241">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="G241" t="s">
-        <v>135</v>
+        <v>336</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D242" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E242" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F242">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="G242" t="s">
-        <v>349</v>
+        <v>63</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B243" t="s">
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D243" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E243" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F243">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G243" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
+        <v>252</v>
+      </c>
+      <c r="B244" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" t="s">
         <v>254</v>
       </c>
-      <c r="B244" t="s">
-        <v>7</v>
-      </c>
-      <c r="C244" t="s">
-        <v>278</v>
-      </c>
       <c r="D244" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E244" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F244">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G244" t="s">
-        <v>306</v>
+        <v>174</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="D245" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E245" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F245">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G245" t="s">
-        <v>253</v>
+        <v>174</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B246" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C246" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D246" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E246" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F246">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G246" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B247" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C247" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D247" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E247" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="F247">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="G247" t="s">
-        <v>380</v>
+        <v>288</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E248" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F248">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G248" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B249" t="s">
         <v>7</v>
       </c>
       <c r="C249" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="D249" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E249" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F249">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="G249" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B250" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C250" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D250" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="E250" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F250">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="G250" t="s">
-        <v>63</v>
+        <v>290</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B251" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C251" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="D251" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E251" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F251">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G251" t="s">
-        <v>381</v>
+        <v>316</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B252" t="s">
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="D252" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E252" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F252">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G252" t="s">
-        <v>338</v>
+        <v>229</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B253" t="s">
         <v>55</v>
       </c>
       <c r="C253" t="s">
-        <v>287</v>
+        <v>66</v>
       </c>
       <c r="D253" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E253" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F253">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="G253" t="s">
-        <v>287</v>
+        <v>66</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C254" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="D254" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E254" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F254">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G254" t="s">
-        <v>288</v>
+        <v>376</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B255" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C255" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="D255" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E255" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F255">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G255" t="s">
-        <v>289</v>
+        <v>355</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B256" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C256" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="D256" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E256" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F256">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G256" t="s">
-        <v>290</v>
+        <v>376</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B257" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C257" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="D257" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E257" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F257">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G257" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B258" t="s">
         <v>55</v>
@@ -7453,13 +7452,13 @@
         <v>292</v>
       </c>
       <c r="D258" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="E258" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F258">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="G258" t="s">
         <v>292</v>
@@ -7467,519 +7466,519 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B259" t="s">
         <v>55</v>
       </c>
       <c r="C259" t="s">
-        <v>66</v>
+        <v>293</v>
       </c>
       <c r="D259" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="E259" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="F259">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="G259" t="s">
-        <v>66</v>
+        <v>293</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B260" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C260" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="D260" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E260" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="F260">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>293</v>
+        <v>371</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B261" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C261" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="D261" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E261" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F261">
-        <v>8</v>
+        <v>175</v>
       </c>
       <c r="G261" t="s">
-        <v>294</v>
+        <v>372</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B262" t="s">
         <v>55</v>
       </c>
       <c r="C262" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D262" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E262" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F262">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="G262" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B263" t="s">
         <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D263" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E263" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F263">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G263" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B264" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C264" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="D264" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F264">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="G264" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B265" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C265" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="D265" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="E265" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="F265">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G265" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B266" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C266" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="D266" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="E266" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="F266">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="G266" t="s">
-        <v>244</v>
+        <v>70</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B267" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C267" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="D267" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="E267" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F267">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="G267" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B268" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="D268" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="E268" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F268">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G268" t="s">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B269" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C269" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="D269" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E269" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F269">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G269" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B270" t="s">
         <v>55</v>
       </c>
       <c r="C270" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D270" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E270" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F270">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G270" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B271" t="s">
         <v>55</v>
       </c>
       <c r="C271" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D271" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="E271" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="F271">
         <v>4</v>
       </c>
       <c r="G271" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B272" t="s">
         <v>55</v>
       </c>
       <c r="C272" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D272" t="s">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="E272" t="s">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="F272">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G272" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B273" t="s">
         <v>55</v>
       </c>
       <c r="C273" t="s">
-        <v>304</v>
+        <v>242</v>
       </c>
       <c r="D273" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E273" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="F273">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G273" t="s">
-        <v>304</v>
+        <v>242</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B274" t="s">
         <v>55</v>
       </c>
       <c r="C274" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D274" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="E274" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F274">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G274" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B275" t="s">
         <v>55</v>
       </c>
       <c r="C275" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D275" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="E275" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="F275">
         <v>6</v>
       </c>
       <c r="G275" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B276" t="s">
         <v>55</v>
       </c>
       <c r="C276" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D276" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E276" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="F276">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G276" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="B277" t="s">
         <v>55</v>
       </c>
       <c r="C277" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D277" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="E277" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G277" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B278" t="s">
         <v>55</v>
       </c>
       <c r="C278" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D278" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="E278" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="F278">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G278" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B279" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C279" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="D279" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="E279" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G279" t="s">
-        <v>382</v>
+        <v>301</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B280" t="s">
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="D280" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E280" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F280">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G280" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B281" t="s">
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="D281" t="s">
         <v>37</v>
@@ -7988,473 +7987,478 @@
         <v>37</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G281" t="s">
-        <v>304</v>
+        <v>360</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B282" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C282" t="s">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="D282" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E282" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="F282">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G282" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B283" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C283" t="s">
-        <v>312</v>
+        <v>274</v>
       </c>
       <c r="D283" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E283" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G283" t="s">
-        <v>312</v>
+        <v>347</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B284" t="s">
         <v>55</v>
       </c>
       <c r="C284" t="s">
-        <v>247</v>
+        <v>302</v>
       </c>
       <c r="D284" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="E284" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="F284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G284" t="s">
-        <v>247</v>
+        <v>302</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D285" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E285" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G285" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B286" t="s">
         <v>7</v>
       </c>
       <c r="C286" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="D286" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E286" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F286">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G286" t="s">
-        <v>383</v>
+        <v>305</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B287" t="s">
         <v>7</v>
       </c>
       <c r="C287" t="s">
-        <v>315</v>
+        <v>276</v>
       </c>
       <c r="D287" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E287" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G287" t="s">
-        <v>370</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B288" t="s">
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="D288" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E288" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F288">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G288" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B289" t="s">
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>317</v>
+        <v>278</v>
       </c>
       <c r="D289" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="E289" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B290" t="s">
         <v>55</v>
       </c>
       <c r="C290" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="D290" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="E290" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F290">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G290" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B291" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C291" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="D291" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E291" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F291">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G291" t="s">
-        <v>384</v>
+        <v>305</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B292" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C292" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
       <c r="D292" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E292" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G292" t="s">
-        <v>320</v>
+        <v>378</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B293" t="s">
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="D293" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E293" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G293" t="s">
-        <v>178</v>
+        <v>336</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="B294" t="s">
         <v>7</v>
       </c>
       <c r="C294" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="D294" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E294" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F294">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="G294" t="s">
-        <v>179</v>
+        <v>336</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B295" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C295" t="s">
-        <v>331</v>
+        <v>148</v>
       </c>
       <c r="D295" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E295" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F295">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G295" t="s">
-        <v>331</v>
+        <v>60</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B296" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C296" t="s">
-        <v>323</v>
+        <v>258</v>
       </c>
       <c r="D296" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="E296" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G296" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B297" t="s">
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D297" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E297" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F297">
         <v>0</v>
       </c>
       <c r="G297" t="s">
-        <v>175</v>
+        <v>382</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B298" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C298" t="s">
-        <v>325</v>
+        <v>60</v>
       </c>
       <c r="D298" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="E298" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G298" t="s">
-        <v>338</v>
+        <v>60</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="B299" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C299" t="s">
-        <v>326</v>
+        <v>289</v>
       </c>
       <c r="D299" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="E299" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G299" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B300" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C300" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="D300" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E300" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F300">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G300" t="s">
-        <v>385</v>
+        <v>291</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>6</v>
+        <v>252</v>
       </c>
       <c r="B301" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C301" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="D301" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="E301" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="F301">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G301" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G301">
+    <sortCondition ref="A2:A301"/>
+    <sortCondition ref="D2:D301"/>
+    <sortCondition ref="B2:B301"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879F60D5-064C-44F7-9358-F8CF2F8BF9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2B4C01-2F8B-427A-84FB-5ADB0A15E8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6141,7 +6141,7 @@
         <v>212</v>
       </c>
       <c r="D201" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E201" t="s">
         <v>29</v>
@@ -6164,7 +6164,7 @@
         <v>213</v>
       </c>
       <c r="D202" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E202" t="s">
         <v>29</v>
@@ -7590,7 +7590,7 @@
         <v>266</v>
       </c>
       <c r="D264" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E264" t="s">
         <v>29</v>

--- a/Master_Drafted_Assets.xlsx
+++ b/Master_Drafted_Assets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smeredith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2B4C01-2F8B-427A-84FB-5ADB0A15E8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5200B9-E641-43B3-B565-41712630BB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="11360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="388">
   <si>
     <t>Manager</t>
   </si>
@@ -701,9 +701,6 @@
     <t>Alex Ovechkin</t>
   </si>
   <si>
-    <t>Andrei Vasilevskiy</t>
-  </si>
-  <si>
     <t>Aleksander Barkov</t>
   </si>
   <si>
@@ -1194,6 +1191,12 @@
   </si>
   <si>
     <t>Philadelphia Flyers</t>
+  </si>
+  <si>
+    <t>Jason Robertson</t>
+  </si>
+  <si>
+    <t>Dallas Stars</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1576,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1607,7 +1610,7 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -1619,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1642,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1665,7 +1668,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1722,7 +1725,7 @@
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1734,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1803,7 +1806,7 @@
         <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1849,7 +1852,7 @@
         <v>76</v>
       </c>
       <c r="G14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1918,7 +1921,7 @@
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1929,7 +1932,7 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -1941,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2033,7 +2036,7 @@
         <v>101</v>
       </c>
       <c r="G22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -2079,7 +2082,7 @@
         <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2159,7 +2162,7 @@
         <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D28" t="s">
         <v>127</v>
@@ -2171,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2274,7 +2277,7 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D33" t="s">
         <v>132</v>
@@ -2286,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -2297,7 +2300,7 @@
         <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D34" t="s">
         <v>132</v>
@@ -2309,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2332,7 +2335,7 @@
         <v>72</v>
       </c>
       <c r="G35" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2355,7 +2358,7 @@
         <v>68</v>
       </c>
       <c r="G36" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2389,7 +2392,7 @@
         <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D38" t="s">
         <v>37</v>
@@ -2401,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -2608,7 +2611,7 @@
         <v>71</v>
       </c>
       <c r="G47" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2654,7 +2657,7 @@
         <v>41</v>
       </c>
       <c r="G49" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -2803,7 +2806,7 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D56" t="s">
         <v>62</v>
@@ -2849,7 +2852,7 @@
         <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D58" t="s">
         <v>62</v>
@@ -2861,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2884,7 +2887,7 @@
         <v>76</v>
       </c>
       <c r="G59" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2930,7 +2933,7 @@
         <v>18</v>
       </c>
       <c r="G61" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2953,7 +2956,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -2964,7 +2967,7 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
@@ -3045,7 +3048,7 @@
         <v>100</v>
       </c>
       <c r="G66" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -3068,7 +3071,7 @@
         <v>25</v>
       </c>
       <c r="G67" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -3079,7 +3082,7 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D68" t="s">
         <v>89</v>
@@ -3091,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -3160,7 +3163,7 @@
         <v>50</v>
       </c>
       <c r="G71" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -3183,7 +3186,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
@@ -3252,7 +3255,7 @@
         <v>200</v>
       </c>
       <c r="G75" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -3275,7 +3278,7 @@
         <v>100</v>
       </c>
       <c r="G76" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -3298,7 +3301,7 @@
         <v>50</v>
       </c>
       <c r="G77" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
@@ -3321,7 +3324,7 @@
         <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -3390,7 +3393,7 @@
         <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
@@ -3413,7 +3416,7 @@
         <v>5</v>
       </c>
       <c r="G82" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -3447,7 +3450,7 @@
         <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D84" t="s">
         <v>155</v>
@@ -3459,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -3470,7 +3473,7 @@
         <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D85" t="s">
         <v>155</v>
@@ -3482,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
@@ -3528,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="G87" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -3539,7 +3542,7 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D88" t="s">
         <v>32</v>
@@ -3551,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -3562,7 +3565,7 @@
         <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D89" t="s">
         <v>32</v>
@@ -3654,7 +3657,7 @@
         <v>55</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D93" t="s">
         <v>127</v>
@@ -3666,7 +3669,7 @@
         <v>50</v>
       </c>
       <c r="G93" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
@@ -3850,7 +3853,7 @@
         <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -3896,7 +3899,7 @@
         <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
@@ -3965,7 +3968,7 @@
         <v>20</v>
       </c>
       <c r="G106" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
@@ -3988,7 +3991,7 @@
         <v>50</v>
       </c>
       <c r="G107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -4034,7 +4037,7 @@
         <v>25</v>
       </c>
       <c r="G109" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -4103,7 +4106,7 @@
         <v>100</v>
       </c>
       <c r="G112" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -4126,7 +4129,7 @@
         <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -4137,7 +4140,7 @@
         <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D114" t="s">
         <v>46</v>
@@ -4149,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
@@ -4264,7 +4267,7 @@
         <v>50</v>
       </c>
       <c r="G119" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
@@ -4287,7 +4290,7 @@
         <v>5</v>
       </c>
       <c r="G120" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
@@ -4333,7 +4336,7 @@
         <v>90</v>
       </c>
       <c r="G122" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
@@ -4379,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
@@ -4425,7 +4428,7 @@
         <v>5</v>
       </c>
       <c r="G126" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -4448,7 +4451,7 @@
         <v>25</v>
       </c>
       <c r="G127" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
@@ -4471,7 +4474,7 @@
         <v>17</v>
       </c>
       <c r="G128" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
@@ -4551,7 +4554,7 @@
         <v>55</v>
       </c>
       <c r="C132" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D132" t="s">
         <v>12</v>
@@ -4563,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
@@ -4609,7 +4612,7 @@
         <v>10</v>
       </c>
       <c r="G134" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
@@ -4655,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -4724,7 +4727,7 @@
         <v>30</v>
       </c>
       <c r="G139" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -4770,7 +4773,7 @@
         <v>5</v>
       </c>
       <c r="G141" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -4793,7 +4796,7 @@
         <v>90</v>
       </c>
       <c r="G142" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
@@ -4816,7 +4819,7 @@
         <v>25</v>
       </c>
       <c r="G143" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
@@ -4839,7 +4842,7 @@
         <v>10</v>
       </c>
       <c r="G144" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
@@ -4862,7 +4865,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
@@ -5115,7 +5118,7 @@
         <v>80</v>
       </c>
       <c r="G156" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5138,7 +5141,7 @@
         <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
@@ -5161,7 +5164,7 @@
         <v>11</v>
       </c>
       <c r="G158" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
@@ -5184,7 +5187,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
@@ -5253,7 +5256,7 @@
         <v>2</v>
       </c>
       <c r="G162" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
@@ -5264,7 +5267,7 @@
         <v>7</v>
       </c>
       <c r="C163" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D163" t="s">
         <v>41</v>
@@ -5276,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
@@ -5299,7 +5302,7 @@
         <v>170</v>
       </c>
       <c r="G164" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
@@ -5322,7 +5325,7 @@
         <v>169</v>
       </c>
       <c r="G165" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
@@ -5391,7 +5394,7 @@
         <v>30</v>
       </c>
       <c r="G168" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5414,7 +5417,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5437,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -5460,7 +5463,7 @@
         <v>90</v>
       </c>
       <c r="G171" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
@@ -5517,7 +5520,7 @@
         <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D174" t="s">
         <v>62</v>
@@ -5667,7 +5670,7 @@
         <v>141</v>
       </c>
       <c r="G180" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
@@ -5690,7 +5693,7 @@
         <v>12</v>
       </c>
       <c r="G181" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
@@ -5701,7 +5704,7 @@
         <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D182" t="s">
         <v>50</v>
@@ -5724,7 +5727,7 @@
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D183" t="s">
         <v>50</v>
@@ -5736,7 +5739,7 @@
         <v>15</v>
       </c>
       <c r="G183" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -5782,7 +5785,7 @@
         <v>50</v>
       </c>
       <c r="G185" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
@@ -5793,7 +5796,7 @@
         <v>55</v>
       </c>
       <c r="C186" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D186" t="s">
         <v>89</v>
@@ -5805,7 +5808,7 @@
         <v>100</v>
       </c>
       <c r="G186" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -5816,7 +5819,7 @@
         <v>55</v>
       </c>
       <c r="C187" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D187" t="s">
         <v>12</v>
@@ -5828,7 +5831,7 @@
         <v>20</v>
       </c>
       <c r="G187" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -5839,7 +5842,7 @@
         <v>55</v>
       </c>
       <c r="C188" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D188" t="s">
         <v>12</v>
@@ -5851,7 +5854,7 @@
         <v>20</v>
       </c>
       <c r="G188" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
@@ -5874,7 +5877,7 @@
         <v>80</v>
       </c>
       <c r="G189" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
@@ -5897,7 +5900,7 @@
         <v>80</v>
       </c>
       <c r="G190" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
@@ -5954,7 +5957,7 @@
         <v>55</v>
       </c>
       <c r="C193" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D193" t="s">
         <v>23</v>
@@ -5966,7 +5969,7 @@
         <v>30</v>
       </c>
       <c r="G193" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
@@ -5977,7 +5980,7 @@
         <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D194" t="s">
         <v>23</v>
@@ -5989,7 +5992,7 @@
         <v>25</v>
       </c>
       <c r="G194" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
@@ -6035,7 +6038,7 @@
         <v>75</v>
       </c>
       <c r="G196" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
@@ -6058,7 +6061,7 @@
         <v>30</v>
       </c>
       <c r="G197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
@@ -6081,7 +6084,7 @@
         <v>30</v>
       </c>
       <c r="G198" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
@@ -6092,7 +6095,7 @@
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -6104,7 +6107,7 @@
         <v>100</v>
       </c>
       <c r="G199" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
@@ -6115,7 +6118,7 @@
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -6127,7 +6130,7 @@
         <v>75</v>
       </c>
       <c r="G200" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
@@ -6150,7 +6153,7 @@
         <v>30</v>
       </c>
       <c r="G201" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
@@ -6219,7 +6222,7 @@
         <v>30</v>
       </c>
       <c r="G204" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
@@ -6242,7 +6245,7 @@
         <v>40</v>
       </c>
       <c r="G205" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
@@ -6253,7 +6256,7 @@
         <v>7</v>
       </c>
       <c r="C206" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
@@ -6265,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="G206" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
@@ -6276,7 +6279,7 @@
         <v>55</v>
       </c>
       <c r="C207" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
@@ -6288,7 +6291,7 @@
         <v>25</v>
       </c>
       <c r="G207" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
@@ -6299,7 +6302,7 @@
         <v>55</v>
       </c>
       <c r="C208" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D208" t="s">
         <v>32</v>
@@ -6311,7 +6314,7 @@
         <v>50</v>
       </c>
       <c r="G208" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
@@ -6322,7 +6325,7 @@
         <v>55</v>
       </c>
       <c r="C209" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D209" t="s">
         <v>73</v>
@@ -6334,7 +6337,7 @@
         <v>40</v>
       </c>
       <c r="G209" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
@@ -6345,7 +6348,7 @@
         <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D210" t="s">
         <v>127</v>
@@ -6357,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="G210" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
@@ -6368,7 +6371,7 @@
         <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D211" t="s">
         <v>75</v>
@@ -6380,7 +6383,7 @@
         <v>10</v>
       </c>
       <c r="G211" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
@@ -6391,7 +6394,7 @@
         <v>55</v>
       </c>
       <c r="C212" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D212" t="s">
         <v>75</v>
@@ -6403,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -6414,7 +6417,7 @@
         <v>55</v>
       </c>
       <c r="C213" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D213" t="s">
         <v>78</v>
@@ -6426,7 +6429,7 @@
         <v>10</v>
       </c>
       <c r="G213" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -6437,7 +6440,7 @@
         <v>55</v>
       </c>
       <c r="C214" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D214" t="s">
         <v>78</v>
@@ -6449,7 +6452,7 @@
         <v>10</v>
       </c>
       <c r="G214" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -6460,7 +6463,7 @@
         <v>55</v>
       </c>
       <c r="C215" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D215" t="s">
         <v>132</v>
@@ -6472,7 +6475,7 @@
         <v>100</v>
       </c>
       <c r="G215" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6483,7 +6486,7 @@
         <v>55</v>
       </c>
       <c r="C216" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D216" t="s">
         <v>132</v>
@@ -6495,7 +6498,7 @@
         <v>75</v>
       </c>
       <c r="G216" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
@@ -6518,7 +6521,7 @@
         <v>80</v>
       </c>
       <c r="G217" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
@@ -6587,7 +6590,7 @@
         <v>25</v>
       </c>
       <c r="G220" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -6598,7 +6601,7 @@
         <v>55</v>
       </c>
       <c r="C221" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D221" t="s">
         <v>37</v>
@@ -6610,7 +6613,7 @@
         <v>60</v>
       </c>
       <c r="G221" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -6621,7 +6624,7 @@
         <v>55</v>
       </c>
       <c r="C222" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D222" t="s">
         <v>37</v>
@@ -6633,7 +6636,7 @@
         <v>40</v>
       </c>
       <c r="G222" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
@@ -6656,7 +6659,7 @@
         <v>35</v>
       </c>
       <c r="G223" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
@@ -6667,7 +6670,7 @@
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>222</v>
+        <v>386</v>
       </c>
       <c r="D224" t="s">
         <v>41</v>
@@ -6679,7 +6682,7 @@
         <v>30</v>
       </c>
       <c r="G224" t="s">
-        <v>251</v>
+        <v>387</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -6690,7 +6693,7 @@
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D225" t="s">
         <v>41</v>
@@ -6713,7 +6716,7 @@
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D226" t="s">
         <v>41</v>
@@ -6725,7 +6728,7 @@
         <v>10</v>
       </c>
       <c r="G226" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -6736,7 +6739,7 @@
         <v>55</v>
       </c>
       <c r="C227" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D227" t="s">
         <v>41</v>
@@ -6748,7 +6751,7 @@
         <v>40</v>
       </c>
       <c r="G227" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6759,7 +6762,7 @@
         <v>55</v>
       </c>
       <c r="C228" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D228" t="s">
         <v>41</v>
@@ -6771,7 +6774,7 @@
         <v>40</v>
       </c>
       <c r="G228" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -6782,7 +6785,7 @@
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D229" t="s">
         <v>46</v>
@@ -6805,7 +6808,7 @@
         <v>7</v>
       </c>
       <c r="C230" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D230" t="s">
         <v>46</v>
@@ -6817,7 +6820,7 @@
         <v>10</v>
       </c>
       <c r="G230" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
@@ -6828,7 +6831,7 @@
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D231" t="s">
         <v>46</v>
@@ -6863,7 +6866,7 @@
         <v>70</v>
       </c>
       <c r="G232" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
@@ -6886,7 +6889,7 @@
         <v>50</v>
       </c>
       <c r="G233" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
@@ -6909,7 +6912,7 @@
         <v>2</v>
       </c>
       <c r="G234" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -6920,7 +6923,7 @@
         <v>55</v>
       </c>
       <c r="C235" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D235" t="s">
         <v>17</v>
@@ -6932,7 +6935,7 @@
         <v>300</v>
       </c>
       <c r="G235" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -6943,7 +6946,7 @@
         <v>55</v>
       </c>
       <c r="C236" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D236" t="s">
         <v>17</v>
@@ -6955,7 +6958,7 @@
         <v>75</v>
       </c>
       <c r="G236" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -6966,7 +6969,7 @@
         <v>55</v>
       </c>
       <c r="C237" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D237" t="s">
         <v>17</v>
@@ -6978,7 +6981,7 @@
         <v>55</v>
       </c>
       <c r="G237" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7001,7 +7004,7 @@
         <v>1</v>
       </c>
       <c r="G238" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7035,7 +7038,7 @@
         <v>55</v>
       </c>
       <c r="C240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D240" t="s">
         <v>67</v>
@@ -7047,7 +7050,7 @@
         <v>20</v>
       </c>
       <c r="G240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
@@ -7058,7 +7061,7 @@
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D241" t="s">
         <v>53</v>
@@ -7070,18 +7073,18 @@
         <v>25</v>
       </c>
       <c r="G241" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B242" t="s">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D242" t="s">
         <v>50</v>
@@ -7098,13 +7101,13 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B243" t="s">
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D243" t="s">
         <v>50</v>
@@ -7116,18 +7119,18 @@
         <v>44</v>
       </c>
       <c r="G243" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B244" t="s">
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D244" t="s">
         <v>9</v>
@@ -7144,13 +7147,13 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D245" t="s">
         <v>9</v>
@@ -7167,13 +7170,13 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B246" t="s">
         <v>55</v>
       </c>
       <c r="C246" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D246" t="s">
         <v>9</v>
@@ -7185,18 +7188,18 @@
         <v>27</v>
       </c>
       <c r="G246" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B247" t="s">
         <v>55</v>
       </c>
       <c r="C247" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D247" t="s">
         <v>9</v>
@@ -7208,18 +7211,18 @@
         <v>16</v>
       </c>
       <c r="G247" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B248" t="s">
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D248" t="s">
         <v>89</v>
@@ -7231,18 +7234,18 @@
         <v>33</v>
       </c>
       <c r="G248" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B249" t="s">
         <v>7</v>
       </c>
       <c r="C249" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
         <v>89</v>
@@ -7254,18 +7257,18 @@
         <v>125</v>
       </c>
       <c r="G249" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B250" t="s">
         <v>55</v>
       </c>
       <c r="C250" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D250" t="s">
         <v>89</v>
@@ -7277,18 +7280,18 @@
         <v>92</v>
       </c>
       <c r="G250" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B251" t="s">
         <v>55</v>
       </c>
       <c r="C251" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D251" t="s">
         <v>89</v>
@@ -7300,18 +7303,18 @@
         <v>0</v>
       </c>
       <c r="G251" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>7</v>
+      </c>
+      <c r="C252" t="s">
         <v>252</v>
-      </c>
-      <c r="B252" t="s">
-        <v>7</v>
-      </c>
-      <c r="C252" t="s">
-        <v>253</v>
       </c>
       <c r="D252" t="s">
         <v>12</v>
@@ -7323,12 +7326,12 @@
         <v>33</v>
       </c>
       <c r="G252" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B253" t="s">
         <v>55</v>
@@ -7351,13 +7354,13 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B254" t="s">
         <v>7</v>
       </c>
       <c r="C254" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>23</v>
@@ -7369,18 +7372,18 @@
         <v>16</v>
       </c>
       <c r="G254" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B255" t="s">
         <v>7</v>
       </c>
       <c r="C255" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D255" t="s">
         <v>23</v>
@@ -7392,18 +7395,18 @@
         <v>3</v>
       </c>
       <c r="G255" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B256" t="s">
         <v>7</v>
       </c>
       <c r="C256" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D256" t="s">
         <v>23</v>
@@ -7415,18 +7418,18 @@
         <v>2</v>
       </c>
       <c r="G256" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B257" t="s">
         <v>7</v>
       </c>
       <c r="C257" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D257" t="s">
         <v>23</v>
@@ -7438,18 +7441,18 @@
         <v>2</v>
       </c>
       <c r="G257" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B258" t="s">
         <v>55</v>
       </c>
       <c r="C258" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D258" t="s">
         <v>23</v>
@@ -7461,18 +7464,18 @@
         <v>8</v>
       </c>
       <c r="G258" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B259" t="s">
         <v>55</v>
       </c>
       <c r="C259" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D259" t="s">
         <v>23</v>
@@ -7484,18 +7487,18 @@
         <v>3</v>
       </c>
       <c r="G259" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B260" t="s">
         <v>7</v>
       </c>
       <c r="C260" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D260" t="s">
         <v>15</v>
@@ -7507,18 +7510,18 @@
         <v>7</v>
       </c>
       <c r="G260" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B261" t="s">
         <v>7</v>
       </c>
       <c r="C261" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D261" t="s">
         <v>15</v>
@@ -7530,18 +7533,18 @@
         <v>175</v>
       </c>
       <c r="G261" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B262" t="s">
         <v>55</v>
       </c>
       <c r="C262" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D262" t="s">
         <v>15</v>
@@ -7553,18 +7556,18 @@
         <v>57</v>
       </c>
       <c r="G262" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B263" t="s">
         <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D263" t="s">
         <v>15</v>
@@ -7576,18 +7579,18 @@
         <v>49</v>
       </c>
       <c r="G263" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B264" t="s">
         <v>7</v>
       </c>
       <c r="C264" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D264" t="s">
         <v>28</v>
@@ -7599,18 +7602,18 @@
         <v>175</v>
       </c>
       <c r="G264" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B265" t="s">
         <v>7</v>
       </c>
       <c r="C265" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D265" t="s">
         <v>155</v>
@@ -7622,18 +7625,18 @@
         <v>18</v>
       </c>
       <c r="G265" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B266" t="s">
         <v>7</v>
       </c>
       <c r="C266" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D266" t="s">
         <v>32</v>
@@ -7650,13 +7653,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B267" t="s">
         <v>7</v>
       </c>
       <c r="C267" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D267" t="s">
         <v>32</v>
@@ -7668,18 +7671,18 @@
         <v>11</v>
       </c>
       <c r="G267" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B268" t="s">
         <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D268" t="s">
         <v>32</v>
@@ -7691,18 +7694,18 @@
         <v>4</v>
       </c>
       <c r="G268" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B269" t="s">
         <v>7</v>
       </c>
       <c r="C269" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D269" t="s">
         <v>32</v>
@@ -7714,18 +7717,18 @@
         <v>2</v>
       </c>
       <c r="G269" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B270" t="s">
         <v>55</v>
       </c>
       <c r="C270" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D270" t="s">
         <v>32</v>
@@ -7737,18 +7740,18 @@
         <v>13</v>
       </c>
       <c r="G270" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B271" t="s">
         <v>55</v>
       </c>
       <c r="C271" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D271" t="s">
         <v>32</v>
@@ -7760,18 +7763,18 @@
         <v>4</v>
       </c>
       <c r="G271" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B272" t="s">
         <v>55</v>
       </c>
       <c r="C272" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D272" t="s">
         <v>73</v>
@@ -7783,18 +7786,18 @@
         <v>23</v>
       </c>
       <c r="G272" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B273" t="s">
         <v>55</v>
       </c>
       <c r="C273" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D273" t="s">
         <v>127</v>
@@ -7806,18 +7809,18 @@
         <v>5</v>
       </c>
       <c r="G273" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B274" t="s">
         <v>55</v>
       </c>
       <c r="C274" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D274" t="s">
         <v>75</v>
@@ -7829,18 +7832,18 @@
         <v>47</v>
       </c>
       <c r="G274" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B275" t="s">
         <v>55</v>
       </c>
       <c r="C275" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D275" t="s">
         <v>75</v>
@@ -7852,18 +7855,18 @@
         <v>6</v>
       </c>
       <c r="G275" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B276" t="s">
         <v>55</v>
       </c>
       <c r="C276" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D276" t="s">
         <v>78</v>
@@ -7875,18 +7878,18 @@
         <v>18</v>
       </c>
       <c r="G276" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B277" t="s">
         <v>55</v>
       </c>
       <c r="C277" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D277" t="s">
         <v>78</v>
@@ -7898,18 +7901,18 @@
         <v>17</v>
       </c>
       <c r="G277" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B278" t="s">
         <v>55</v>
       </c>
       <c r="C278" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D278" t="s">
         <v>132</v>
@@ -7921,18 +7924,18 @@
         <v>4</v>
       </c>
       <c r="G278" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B279" t="s">
         <v>55</v>
       </c>
       <c r="C279" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D279" t="s">
         <v>132</v>
@@ -7944,18 +7947,18 @@
         <v>1</v>
       </c>
       <c r="G279" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B280" t="s">
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D280" t="s">
         <v>37</v>
@@ -7972,13 +7975,13 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B281" t="s">
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D281" t="s">
         <v>37</v>
@@ -7990,18 +7993,18 @@
         <v>8</v>
       </c>
       <c r="G281" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B282" t="s">
         <v>7</v>
       </c>
       <c r="C282" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D282" t="s">
         <v>37</v>
@@ -8018,13 +8021,13 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B283" t="s">
         <v>7</v>
       </c>
       <c r="C283" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D283" t="s">
         <v>37</v>
@@ -8036,18 +8039,18 @@
         <v>11</v>
       </c>
       <c r="G283" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B284" t="s">
         <v>55</v>
       </c>
       <c r="C284" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D284" t="s">
         <v>37</v>
@@ -8059,18 +8062,18 @@
         <v>1</v>
       </c>
       <c r="G284" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B285" t="s">
         <v>55</v>
       </c>
       <c r="C285" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D285" t="s">
         <v>37</v>
@@ -8082,18 +8085,18 @@
         <v>1</v>
       </c>
       <c r="G285" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B286" t="s">
         <v>7</v>
       </c>
       <c r="C286" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D286" t="s">
         <v>41</v>
@@ -8105,18 +8108,18 @@
         <v>55</v>
       </c>
       <c r="G286" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B287" t="s">
         <v>7</v>
       </c>
       <c r="C287" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D287" t="s">
         <v>41</v>
@@ -8128,18 +8131,18 @@
         <v>11</v>
       </c>
       <c r="G287" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B288" t="s">
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D288" t="s">
         <v>41</v>
@@ -8151,18 +8154,18 @@
         <v>4</v>
       </c>
       <c r="G288" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B289" t="s">
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D289" t="s">
         <v>41</v>
@@ -8174,18 +8177,18 @@
         <v>1</v>
       </c>
       <c r="G289" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B290" t="s">
         <v>55</v>
       </c>
       <c r="C290" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D290" t="s">
         <v>41</v>
@@ -8197,18 +8200,18 @@
         <v>6</v>
       </c>
       <c r="G290" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B291" t="s">
         <v>55</v>
       </c>
       <c r="C291" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D291" t="s">
         <v>41</v>
@@ -8220,18 +8223,18 @@
         <v>5</v>
       </c>
       <c r="G291" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B292" t="s">
         <v>7</v>
       </c>
       <c r="C292" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D292" t="s">
         <v>46</v>
@@ -8243,18 +8246,18 @@
         <v>87</v>
       </c>
       <c r="G292" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B293" t="s">
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D293" t="s">
         <v>46</v>
@@ -8266,18 +8269,18 @@
         <v>2</v>
       </c>
       <c r="G293" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B294" t="s">
         <v>7</v>
       </c>
       <c r="C294" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D294" t="s">
         <v>46</v>
@@ -8289,12 +8292,12 @@
         <v>175</v>
       </c>
       <c r="G294" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B295" t="s">
         <v>7</v>
@@ -8317,13 +8320,13 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B296" t="s">
         <v>7</v>
       </c>
       <c r="C296" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D296" t="s">
         <v>17</v>
@@ -8335,18 +8338,18 @@
         <v>42</v>
       </c>
       <c r="G296" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B297" t="s">
         <v>7</v>
       </c>
       <c r="C297" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D297" t="s">
         <v>17</v>
@@ -8358,12 +8361,12 @@
         <v>0</v>
       </c>
       <c r="G297" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B298" t="s">
         <v>55</v>
@@ -8386,13 +8389,13 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B299" t="s">
         <v>55</v>
       </c>
       <c r="C299" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D299" t="s">
         <v>17</v>
@@ -8404,18 +8407,18 @@
         <v>51</v>
       </c>
       <c r="G299" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B300" t="s">
         <v>55</v>
       </c>
       <c r="C300" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D300" t="s">
         <v>67</v>
@@ -8427,18 +8430,18 @@
         <v>3</v>
       </c>
       <c r="G300" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B301" t="s">
         <v>7</v>
       </c>
       <c r="C301" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D301" t="s">
         <v>53</v>
@@ -8450,7 +8453,7 @@
         <v>58</v>
       </c>
       <c r="G301" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
